--- a/template.xlsx
+++ b/template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/100millibar-8/.gemini/antigravity-ide/scratch/radio_allocation/app/dist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21BD509-E1B6-0540-8B4B-A8CD8FB8D8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0C1BF0-71B8-5F46-89B5-95A788CAD2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28460" windowHeight="24880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
